--- a/tests/testData/excelSwag.xlsx
+++ b/tests/testData/excelSwag.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erick.jimenez\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erick.jimenez\Documents\GitHub\PlaywrightRadafirst\tests\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DEF4BBA-7966-4035-A430-1B553850B64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE50B1CD-DDFD-454E-B52D-DCD52A4162E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19305" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{5A902D67-E620-4A64-9BE8-8B74B4EE0AFB}"/>
   </bookViews>
@@ -78,12 +78,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -98,8 +104,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,10 +449,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
